--- a/Final_Model_Metrics_Comparison.xlsx
+++ b/Final_Model_Metrics_Comparison.xlsx
@@ -474,9 +474,6 @@
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
-        <v>0.9885183526463224</v>
-      </c>
       <c r="C7">
         <v>0.9901594306667825</v>
       </c>
@@ -484,9 +481,6 @@
     <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>9</v>
-      </c>
-      <c r="B8">
-        <v>0.1787250061847885</v>
       </c>
       <c r="C8">
         <v>0.1952358527202977</v>
